--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.47838</v>
+        <v>17.4898</v>
       </c>
       <c r="D2" t="n">
-        <v>17.40685</v>
+        <v>17.38818</v>
       </c>
       <c r="E2" t="n">
-        <v>17.29002</v>
+        <v>17.41604</v>
       </c>
       <c r="F2" t="n">
-        <v>45.11183</v>
+        <v>44.21312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05346</v>
+        <v>0.05473</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93544</v>
+        <v>1.91576</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.29355</v>
+        <v>17.83135</v>
       </c>
       <c r="D3" t="n">
-        <v>17.78539</v>
+        <v>17.50901</v>
       </c>
       <c r="E3" t="n">
-        <v>17.595</v>
+        <v>17.6101</v>
       </c>
       <c r="F3" t="n">
-        <v>45.06182</v>
+        <v>45.33027</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05326</v>
+        <v>0.05331</v>
       </c>
       <c r="H3" t="n">
-        <v>1.96408</v>
+        <v>1.92256</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.64767</v>
+        <v>18.0716</v>
       </c>
       <c r="D4" t="n">
-        <v>17.25764</v>
+        <v>17.13049</v>
       </c>
       <c r="E4" t="n">
-        <v>17.76279</v>
+        <v>17.37093</v>
       </c>
       <c r="F4" t="n">
-        <v>44.32802</v>
+        <v>45.09158</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05362</v>
+        <v>0.05275</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94654</v>
+        <v>1.91668</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.10996</v>
+        <v>17.78698</v>
       </c>
       <c r="D6" t="n">
-        <v>16.85572</v>
+        <v>16.51138</v>
       </c>
       <c r="E6" t="n">
-        <v>17.45974</v>
+        <v>17.69181</v>
       </c>
       <c r="F6" t="n">
-        <v>22.80233</v>
+        <v>23.17689</v>
       </c>
       <c r="G6" t="n">
-        <v>36.05237</v>
+        <v>35.77381</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.22142</v>
+        <v>17.50696</v>
       </c>
       <c r="D7" t="n">
-        <v>17.00571</v>
+        <v>16.87671</v>
       </c>
       <c r="E7" t="n">
-        <v>17.42754</v>
+        <v>16.93198</v>
       </c>
       <c r="F7" t="n">
-        <v>23.12521</v>
+        <v>23.38729</v>
       </c>
       <c r="G7" t="n">
-        <v>36.34331</v>
+        <v>36.4828</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.90122</v>
+        <v>17.59647</v>
       </c>
       <c r="D8" t="n">
-        <v>16.91107</v>
+        <v>16.80994</v>
       </c>
       <c r="E8" t="n">
-        <v>17.92109</v>
+        <v>17.37472</v>
       </c>
       <c r="F8" t="n">
-        <v>23.1879</v>
+        <v>22.71651</v>
       </c>
       <c r="G8" t="n">
-        <v>36.06204</v>
+        <v>36.4362</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6486499999999999</v>
+        <v>0.66037</v>
       </c>
       <c r="D10" t="n">
-        <v>1.18891</v>
+        <v>1.17682</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.63813</v>
+        <v>0.6392099999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.16483</v>
+        <v>1.1723</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.63395</v>
+        <v>0.64538</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16106</v>
+        <v>1.17448</v>
       </c>
     </row>
   </sheetData>
